--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -236,10 +236,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
